--- a/de.bund.bfr.knime.openkrise.db/src/de/bund/bfr/knime/openkrise/db/imports/custom/bfrnewformat/FCL_Uptrace_Prod_en.xlsx
+++ b/de.bund.bfr.knime.openkrise.db/src/de/bund/bfr/knime/openkrise/db/imports/custom/bfrnewformat/FCL_Uptrace_Prod_en.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1928BD74-79C0-42B4-86DD-257BB51C1040}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-15" yWindow="5745" windowWidth="25215" windowHeight="5760"/>
+    <workbookView xWindow="1005" yWindow="1995" windowWidth="28695" windowHeight="15075" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Production - Fwdtrace" sheetId="5" r:id="rId1"/>
@@ -12,7 +13,18 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Production - Fwdtrace'!$A$1:$M$48</definedName>
   </definedNames>
-  <calcPr calcId="145621"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -151,22 +163,22 @@
     </r>
   </si>
   <si>
-    <t>For questions please contact the FoodRisk-Labs team, +49 (30) 18412-4444, foodrisklabs@bfr.bund.de</t>
-  </si>
-  <si>
-    <t>Digital extracts (e.g. Excel or XML files) of the company database could also be suitable. In this case you do not need to fill this template - please call us to find a solution (BfR FoodRiskLabs-Team, +49 (30) 18412-4444)</t>
-  </si>
-  <si>
     <t>Then, please assess the data for the next incoming good(s) accordingly.</t>
   </si>
   <si>
     <t>In Column A starting with Line Number x please enter the line number of the incoming good being the ingredient of this product. enter the requested information into columns B onwards.</t>
   </si>
+  <si>
+    <t>For questions please contact the FoodRisk-Labs team via foodrisklabs@bfr.bund.de</t>
+  </si>
+  <si>
+    <t>Digital extracts (e.g. Excel or XML files) of the company database could also be suitable. In this case you do not need to fill this template - please contact us to find a solution.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="39" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1587,6 +1599,24 @@
     <xf numFmtId="1" fontId="3" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="3" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="9" fillId="6" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1624,42 +1654,6 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="3" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="3" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="3" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="49" fontId="9" fillId="6" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1701,6 +1695,24 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="49" fontId="7" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="3" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="3" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="37" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1746,120 +1758,120 @@
     </xf>
   </cellXfs>
   <cellStyles count="114">
-    <cellStyle name="20% - Accent1 2" xfId="4"/>
-    <cellStyle name="20% - Accent2 2" xfId="5"/>
-    <cellStyle name="20% - Accent3 2" xfId="6"/>
-    <cellStyle name="20% - Accent4 2" xfId="7"/>
-    <cellStyle name="20% - Accent5 2" xfId="8"/>
-    <cellStyle name="20% - Accent6 2" xfId="9"/>
-    <cellStyle name="40% - Accent1 2" xfId="10"/>
-    <cellStyle name="40% - Accent2 2" xfId="11"/>
-    <cellStyle name="40% - Accent3 2" xfId="12"/>
-    <cellStyle name="40% - Accent4 2" xfId="13"/>
-    <cellStyle name="40% - Accent5 2" xfId="14"/>
-    <cellStyle name="40% - Accent6 2" xfId="15"/>
-    <cellStyle name="60% - Accent1 2" xfId="16"/>
-    <cellStyle name="60% - Accent2 2" xfId="17"/>
-    <cellStyle name="60% - Accent3 2" xfId="18"/>
-    <cellStyle name="60% - Accent4 2" xfId="19"/>
-    <cellStyle name="60% - Accent5 2" xfId="20"/>
-    <cellStyle name="60% - Accent6 2" xfId="21"/>
-    <cellStyle name="Accent1 2" xfId="22"/>
-    <cellStyle name="Accent2 2" xfId="23"/>
-    <cellStyle name="Accent3 2" xfId="24"/>
-    <cellStyle name="Accent4 2" xfId="25"/>
-    <cellStyle name="Accent5 2" xfId="26"/>
-    <cellStyle name="Accent6 2" xfId="27"/>
-    <cellStyle name="Bad 2" xfId="28"/>
-    <cellStyle name="Calculation 2" xfId="29"/>
-    <cellStyle name="Check Cell 2" xfId="30"/>
-    <cellStyle name="Explanatory Text 2" xfId="31"/>
-    <cellStyle name="Good 2" xfId="32"/>
-    <cellStyle name="Heading 1 2" xfId="33"/>
-    <cellStyle name="Heading 2 2" xfId="34"/>
-    <cellStyle name="Heading 3 2" xfId="35"/>
-    <cellStyle name="Heading 4 2" xfId="36"/>
-    <cellStyle name="Input 2" xfId="37"/>
-    <cellStyle name="Linked Cell 2" xfId="38"/>
-    <cellStyle name="Neutral 2" xfId="39"/>
-    <cellStyle name="Normal 10" xfId="40"/>
-    <cellStyle name="Normal 10 2" xfId="41"/>
-    <cellStyle name="Normal 10 2 2" xfId="42"/>
-    <cellStyle name="Normal 10 2 3" xfId="43"/>
-    <cellStyle name="Normal 10 3" xfId="44"/>
-    <cellStyle name="Normal 10 4" xfId="45"/>
-    <cellStyle name="Normal 11" xfId="46"/>
-    <cellStyle name="Normal 11 2" xfId="47"/>
-    <cellStyle name="Normal 11 2 2" xfId="48"/>
-    <cellStyle name="Normal 11 2 3" xfId="49"/>
-    <cellStyle name="Normal 11 3" xfId="50"/>
-    <cellStyle name="Normal 11 4" xfId="51"/>
-    <cellStyle name="Normal 12" xfId="52"/>
-    <cellStyle name="Normal 12 2" xfId="53"/>
-    <cellStyle name="Normal 12 3" xfId="54"/>
-    <cellStyle name="Normal 12 4" xfId="55"/>
-    <cellStyle name="Normal 13" xfId="56"/>
-    <cellStyle name="Normal 13 2" xfId="57"/>
-    <cellStyle name="Normal 13 3" xfId="58"/>
-    <cellStyle name="Normal 13 4" xfId="59"/>
-    <cellStyle name="Normal 14" xfId="60"/>
-    <cellStyle name="Normal 14 2" xfId="61"/>
-    <cellStyle name="Normal 15" xfId="62"/>
-    <cellStyle name="Normal 15 2" xfId="63"/>
-    <cellStyle name="Normal 16" xfId="64"/>
-    <cellStyle name="Normal 17" xfId="65"/>
-    <cellStyle name="Normal 2" xfId="2"/>
-    <cellStyle name="Normal 2 2" xfId="67"/>
-    <cellStyle name="Normal 2 2 2" xfId="68"/>
-    <cellStyle name="Normal 2 2 3" xfId="69"/>
-    <cellStyle name="Normal 2 3" xfId="70"/>
-    <cellStyle name="Normal 2 3 2" xfId="71"/>
-    <cellStyle name="Normal 2 3 3" xfId="72"/>
-    <cellStyle name="Normal 2 4" xfId="73"/>
-    <cellStyle name="Normal 2 5" xfId="74"/>
-    <cellStyle name="Normal 2 6" xfId="66"/>
-    <cellStyle name="Normal 3" xfId="1"/>
-    <cellStyle name="Normal 3 2" xfId="76"/>
-    <cellStyle name="Normal 3 3" xfId="77"/>
-    <cellStyle name="Normal 3 4" xfId="75"/>
-    <cellStyle name="Normal 4" xfId="78"/>
-    <cellStyle name="Normal 4 2" xfId="79"/>
-    <cellStyle name="Normal 4 3" xfId="80"/>
-    <cellStyle name="Normal 5" xfId="81"/>
-    <cellStyle name="Normal 6" xfId="82"/>
-    <cellStyle name="Normal 6 2" xfId="83"/>
-    <cellStyle name="Normal 6 3" xfId="84"/>
-    <cellStyle name="Normal 7" xfId="85"/>
-    <cellStyle name="Normal 7 2" xfId="86"/>
-    <cellStyle name="Normal 7 2 2" xfId="87"/>
-    <cellStyle name="Normal 7 2 3" xfId="88"/>
-    <cellStyle name="Normal 7 3" xfId="89"/>
-    <cellStyle name="Normal 7 3 2" xfId="90"/>
-    <cellStyle name="Normal 7 3 3" xfId="91"/>
-    <cellStyle name="Normal 7 4" xfId="92"/>
-    <cellStyle name="Normal 7 5" xfId="93"/>
-    <cellStyle name="Normal 8" xfId="94"/>
-    <cellStyle name="Normal 8 2" xfId="95"/>
-    <cellStyle name="Normal 8 2 2" xfId="96"/>
-    <cellStyle name="Normal 8 2 3" xfId="97"/>
-    <cellStyle name="Normal 8 3" xfId="98"/>
-    <cellStyle name="Normal 8 4" xfId="99"/>
-    <cellStyle name="Normal 9" xfId="100"/>
-    <cellStyle name="Normal 9 2" xfId="101"/>
-    <cellStyle name="Normal 9 2 2" xfId="102"/>
-    <cellStyle name="Normal 9 2 3" xfId="103"/>
-    <cellStyle name="Normal 9 3" xfId="104"/>
-    <cellStyle name="Normal 9 4" xfId="105"/>
-    <cellStyle name="Note 2" xfId="106"/>
-    <cellStyle name="Notiz 2" xfId="113"/>
-    <cellStyle name="Output 2" xfId="107"/>
-    <cellStyle name="Standaard_Business_List" xfId="108"/>
+    <cellStyle name="20% - Accent1 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
+    <cellStyle name="20% - Accent2 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="20% - Accent3 2" xfId="6" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="20% - Accent4 2" xfId="7" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="20% - Accent5 2" xfId="8" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="20% - Accent6 2" xfId="9" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
+    <cellStyle name="40% - Accent1 2" xfId="10" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
+    <cellStyle name="40% - Accent2 2" xfId="11" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
+    <cellStyle name="40% - Accent3 2" xfId="12" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
+    <cellStyle name="40% - Accent4 2" xfId="13" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
+    <cellStyle name="40% - Accent5 2" xfId="14" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
+    <cellStyle name="40% - Accent6 2" xfId="15" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
+    <cellStyle name="60% - Accent1 2" xfId="16" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
+    <cellStyle name="60% - Accent2 2" xfId="17" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
+    <cellStyle name="60% - Accent3 2" xfId="18" xr:uid="{00000000-0005-0000-0000-00000E000000}"/>
+    <cellStyle name="60% - Accent4 2" xfId="19" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
+    <cellStyle name="60% - Accent5 2" xfId="20" xr:uid="{00000000-0005-0000-0000-000010000000}"/>
+    <cellStyle name="60% - Accent6 2" xfId="21" xr:uid="{00000000-0005-0000-0000-000011000000}"/>
+    <cellStyle name="Accent1 2" xfId="22" xr:uid="{00000000-0005-0000-0000-000012000000}"/>
+    <cellStyle name="Accent2 2" xfId="23" xr:uid="{00000000-0005-0000-0000-000013000000}"/>
+    <cellStyle name="Accent3 2" xfId="24" xr:uid="{00000000-0005-0000-0000-000014000000}"/>
+    <cellStyle name="Accent4 2" xfId="25" xr:uid="{00000000-0005-0000-0000-000015000000}"/>
+    <cellStyle name="Accent5 2" xfId="26" xr:uid="{00000000-0005-0000-0000-000016000000}"/>
+    <cellStyle name="Accent6 2" xfId="27" xr:uid="{00000000-0005-0000-0000-000017000000}"/>
+    <cellStyle name="Bad 2" xfId="28" xr:uid="{00000000-0005-0000-0000-000018000000}"/>
+    <cellStyle name="Calculation 2" xfId="29" xr:uid="{00000000-0005-0000-0000-000019000000}"/>
+    <cellStyle name="Check Cell 2" xfId="30" xr:uid="{00000000-0005-0000-0000-00001A000000}"/>
+    <cellStyle name="Explanatory Text 2" xfId="31" xr:uid="{00000000-0005-0000-0000-00001B000000}"/>
+    <cellStyle name="Good 2" xfId="32" xr:uid="{00000000-0005-0000-0000-00001C000000}"/>
+    <cellStyle name="Heading 1 2" xfId="33" xr:uid="{00000000-0005-0000-0000-00001D000000}"/>
+    <cellStyle name="Heading 2 2" xfId="34" xr:uid="{00000000-0005-0000-0000-00001E000000}"/>
+    <cellStyle name="Heading 3 2" xfId="35" xr:uid="{00000000-0005-0000-0000-00001F000000}"/>
+    <cellStyle name="Heading 4 2" xfId="36" xr:uid="{00000000-0005-0000-0000-000020000000}"/>
+    <cellStyle name="Input 2" xfId="37" xr:uid="{00000000-0005-0000-0000-000021000000}"/>
+    <cellStyle name="Linked Cell 2" xfId="38" xr:uid="{00000000-0005-0000-0000-000022000000}"/>
+    <cellStyle name="Neutral 2" xfId="39" xr:uid="{00000000-0005-0000-0000-000023000000}"/>
+    <cellStyle name="Normal 10" xfId="40" xr:uid="{00000000-0005-0000-0000-000024000000}"/>
+    <cellStyle name="Normal 10 2" xfId="41" xr:uid="{00000000-0005-0000-0000-000025000000}"/>
+    <cellStyle name="Normal 10 2 2" xfId="42" xr:uid="{00000000-0005-0000-0000-000026000000}"/>
+    <cellStyle name="Normal 10 2 3" xfId="43" xr:uid="{00000000-0005-0000-0000-000027000000}"/>
+    <cellStyle name="Normal 10 3" xfId="44" xr:uid="{00000000-0005-0000-0000-000028000000}"/>
+    <cellStyle name="Normal 10 4" xfId="45" xr:uid="{00000000-0005-0000-0000-000029000000}"/>
+    <cellStyle name="Normal 11" xfId="46" xr:uid="{00000000-0005-0000-0000-00002A000000}"/>
+    <cellStyle name="Normal 11 2" xfId="47" xr:uid="{00000000-0005-0000-0000-00002B000000}"/>
+    <cellStyle name="Normal 11 2 2" xfId="48" xr:uid="{00000000-0005-0000-0000-00002C000000}"/>
+    <cellStyle name="Normal 11 2 3" xfId="49" xr:uid="{00000000-0005-0000-0000-00002D000000}"/>
+    <cellStyle name="Normal 11 3" xfId="50" xr:uid="{00000000-0005-0000-0000-00002E000000}"/>
+    <cellStyle name="Normal 11 4" xfId="51" xr:uid="{00000000-0005-0000-0000-00002F000000}"/>
+    <cellStyle name="Normal 12" xfId="52" xr:uid="{00000000-0005-0000-0000-000030000000}"/>
+    <cellStyle name="Normal 12 2" xfId="53" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="Normal 12 3" xfId="54" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
+    <cellStyle name="Normal 12 4" xfId="55" xr:uid="{00000000-0005-0000-0000-000033000000}"/>
+    <cellStyle name="Normal 13" xfId="56" xr:uid="{00000000-0005-0000-0000-000034000000}"/>
+    <cellStyle name="Normal 13 2" xfId="57" xr:uid="{00000000-0005-0000-0000-000035000000}"/>
+    <cellStyle name="Normal 13 3" xfId="58" xr:uid="{00000000-0005-0000-0000-000036000000}"/>
+    <cellStyle name="Normal 13 4" xfId="59" xr:uid="{00000000-0005-0000-0000-000037000000}"/>
+    <cellStyle name="Normal 14" xfId="60" xr:uid="{00000000-0005-0000-0000-000038000000}"/>
+    <cellStyle name="Normal 14 2" xfId="61" xr:uid="{00000000-0005-0000-0000-000039000000}"/>
+    <cellStyle name="Normal 15" xfId="62" xr:uid="{00000000-0005-0000-0000-00003A000000}"/>
+    <cellStyle name="Normal 15 2" xfId="63" xr:uid="{00000000-0005-0000-0000-00003B000000}"/>
+    <cellStyle name="Normal 16" xfId="64" xr:uid="{00000000-0005-0000-0000-00003C000000}"/>
+    <cellStyle name="Normal 17" xfId="65" xr:uid="{00000000-0005-0000-0000-00003D000000}"/>
+    <cellStyle name="Normal 2" xfId="2" xr:uid="{00000000-0005-0000-0000-00003E000000}"/>
+    <cellStyle name="Normal 2 2" xfId="67" xr:uid="{00000000-0005-0000-0000-00003F000000}"/>
+    <cellStyle name="Normal 2 2 2" xfId="68" xr:uid="{00000000-0005-0000-0000-000040000000}"/>
+    <cellStyle name="Normal 2 2 3" xfId="69" xr:uid="{00000000-0005-0000-0000-000041000000}"/>
+    <cellStyle name="Normal 2 3" xfId="70" xr:uid="{00000000-0005-0000-0000-000042000000}"/>
+    <cellStyle name="Normal 2 3 2" xfId="71" xr:uid="{00000000-0005-0000-0000-000043000000}"/>
+    <cellStyle name="Normal 2 3 3" xfId="72" xr:uid="{00000000-0005-0000-0000-000044000000}"/>
+    <cellStyle name="Normal 2 4" xfId="73" xr:uid="{00000000-0005-0000-0000-000045000000}"/>
+    <cellStyle name="Normal 2 5" xfId="74" xr:uid="{00000000-0005-0000-0000-000046000000}"/>
+    <cellStyle name="Normal 2 6" xfId="66" xr:uid="{00000000-0005-0000-0000-000047000000}"/>
+    <cellStyle name="Normal 3" xfId="1" xr:uid="{00000000-0005-0000-0000-000048000000}"/>
+    <cellStyle name="Normal 3 2" xfId="76" xr:uid="{00000000-0005-0000-0000-000049000000}"/>
+    <cellStyle name="Normal 3 3" xfId="77" xr:uid="{00000000-0005-0000-0000-00004A000000}"/>
+    <cellStyle name="Normal 3 4" xfId="75" xr:uid="{00000000-0005-0000-0000-00004B000000}"/>
+    <cellStyle name="Normal 4" xfId="78" xr:uid="{00000000-0005-0000-0000-00004C000000}"/>
+    <cellStyle name="Normal 4 2" xfId="79" xr:uid="{00000000-0005-0000-0000-00004D000000}"/>
+    <cellStyle name="Normal 4 3" xfId="80" xr:uid="{00000000-0005-0000-0000-00004E000000}"/>
+    <cellStyle name="Normal 5" xfId="81" xr:uid="{00000000-0005-0000-0000-00004F000000}"/>
+    <cellStyle name="Normal 6" xfId="82" xr:uid="{00000000-0005-0000-0000-000050000000}"/>
+    <cellStyle name="Normal 6 2" xfId="83" xr:uid="{00000000-0005-0000-0000-000051000000}"/>
+    <cellStyle name="Normal 6 3" xfId="84" xr:uid="{00000000-0005-0000-0000-000052000000}"/>
+    <cellStyle name="Normal 7" xfId="85" xr:uid="{00000000-0005-0000-0000-000053000000}"/>
+    <cellStyle name="Normal 7 2" xfId="86" xr:uid="{00000000-0005-0000-0000-000054000000}"/>
+    <cellStyle name="Normal 7 2 2" xfId="87" xr:uid="{00000000-0005-0000-0000-000055000000}"/>
+    <cellStyle name="Normal 7 2 3" xfId="88" xr:uid="{00000000-0005-0000-0000-000056000000}"/>
+    <cellStyle name="Normal 7 3" xfId="89" xr:uid="{00000000-0005-0000-0000-000057000000}"/>
+    <cellStyle name="Normal 7 3 2" xfId="90" xr:uid="{00000000-0005-0000-0000-000058000000}"/>
+    <cellStyle name="Normal 7 3 3" xfId="91" xr:uid="{00000000-0005-0000-0000-000059000000}"/>
+    <cellStyle name="Normal 7 4" xfId="92" xr:uid="{00000000-0005-0000-0000-00005A000000}"/>
+    <cellStyle name="Normal 7 5" xfId="93" xr:uid="{00000000-0005-0000-0000-00005B000000}"/>
+    <cellStyle name="Normal 8" xfId="94" xr:uid="{00000000-0005-0000-0000-00005C000000}"/>
+    <cellStyle name="Normal 8 2" xfId="95" xr:uid="{00000000-0005-0000-0000-00005D000000}"/>
+    <cellStyle name="Normal 8 2 2" xfId="96" xr:uid="{00000000-0005-0000-0000-00005E000000}"/>
+    <cellStyle name="Normal 8 2 3" xfId="97" xr:uid="{00000000-0005-0000-0000-00005F000000}"/>
+    <cellStyle name="Normal 8 3" xfId="98" xr:uid="{00000000-0005-0000-0000-000060000000}"/>
+    <cellStyle name="Normal 8 4" xfId="99" xr:uid="{00000000-0005-0000-0000-000061000000}"/>
+    <cellStyle name="Normal 9" xfId="100" xr:uid="{00000000-0005-0000-0000-000062000000}"/>
+    <cellStyle name="Normal 9 2" xfId="101" xr:uid="{00000000-0005-0000-0000-000063000000}"/>
+    <cellStyle name="Normal 9 2 2" xfId="102" xr:uid="{00000000-0005-0000-0000-000064000000}"/>
+    <cellStyle name="Normal 9 2 3" xfId="103" xr:uid="{00000000-0005-0000-0000-000065000000}"/>
+    <cellStyle name="Normal 9 3" xfId="104" xr:uid="{00000000-0005-0000-0000-000066000000}"/>
+    <cellStyle name="Normal 9 4" xfId="105" xr:uid="{00000000-0005-0000-0000-000067000000}"/>
+    <cellStyle name="Note 2" xfId="106" xr:uid="{00000000-0005-0000-0000-000068000000}"/>
+    <cellStyle name="Notiz 2" xfId="113" xr:uid="{00000000-0005-0000-0000-000069000000}"/>
+    <cellStyle name="Output 2" xfId="107" xr:uid="{00000000-0005-0000-0000-00006A000000}"/>
+    <cellStyle name="Standaard_Business_List" xfId="108" xr:uid="{00000000-0005-0000-0000-00006B000000}"/>
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
-    <cellStyle name="Standard 2" xfId="3"/>
-    <cellStyle name="Standard 3" xfId="112"/>
-    <cellStyle name="Title 2" xfId="109"/>
-    <cellStyle name="Total 2" xfId="110"/>
-    <cellStyle name="Warning Text 2" xfId="111"/>
+    <cellStyle name="Standard 2" xfId="3" xr:uid="{00000000-0005-0000-0000-00006D000000}"/>
+    <cellStyle name="Standard 3" xfId="112" xr:uid="{00000000-0005-0000-0000-00006E000000}"/>
+    <cellStyle name="Title 2" xfId="109" xr:uid="{00000000-0005-0000-0000-00006F000000}"/>
+    <cellStyle name="Total 2" xfId="110" xr:uid="{00000000-0005-0000-0000-000070000000}"/>
+    <cellStyle name="Warning Text 2" xfId="111" xr:uid="{00000000-0005-0000-0000-000071000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -1867,14 +1879,17 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Larissa">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
-    <a:clrScheme name="Larissa">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1912,9 +1927,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Larissa">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1947,9 +1962,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1982,9 +2014,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Larissa">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2157,31 +2206,31 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:S49"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.73046875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="24.59765625" style="1" customWidth="1"/>
-    <col min="3" max="4" width="12.3984375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="11.86328125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="4.3984375" style="5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.73046875" style="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.265625" style="5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.86328125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="19.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="24.5703125" style="1" customWidth="1"/>
+    <col min="3" max="4" width="12.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11.85546875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="4.42578125" style="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.7109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.28515625" style="5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" customWidth="1"/>
     <col min="10" max="10" width="23" style="1" customWidth="1"/>
     <col min="11" max="11" width="40" style="1" customWidth="1"/>
-    <col min="12" max="12" width="8.1328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="19.265625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="8.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.28515625" style="1" customWidth="1"/>
     <col min="14" max="14" width="27" style="10" customWidth="1"/>
-    <col min="15" max="18" width="11.3984375" style="10"/>
-    <col min="19" max="16384" width="11.3984375" style="1"/>
+    <col min="15" max="18" width="11.42578125" style="10"/>
+    <col min="19" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="22" customFormat="1" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:19" s="22" customFormat="1" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="101" t="s">
         <v>24</v>
       </c>
@@ -2204,9 +2253,9 @@
       <c r="R1" s="20"/>
       <c r="S1" s="21"/>
     </row>
-    <row r="2" spans="1:19" s="9" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:19" s="9" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="111" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B2" s="112"/>
       <c r="C2" s="112"/>
@@ -2227,58 +2276,58 @@
       <c r="R2" s="8"/>
       <c r="S2" s="7"/>
     </row>
-    <row r="3" spans="1:19" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="66" t="s">
+    <row r="3" spans="1:19" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="67"/>
-      <c r="C3" s="67"/>
-      <c r="D3" s="67"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="67"/>
-      <c r="G3" s="67"/>
-      <c r="H3" s="67"/>
-      <c r="I3" s="67"/>
-      <c r="J3" s="67"/>
-      <c r="K3" s="67"/>
-      <c r="L3" s="67"/>
-      <c r="M3" s="68"/>
+      <c r="B3" s="72"/>
+      <c r="C3" s="72"/>
+      <c r="D3" s="72"/>
+      <c r="E3" s="72"/>
+      <c r="F3" s="72"/>
+      <c r="G3" s="72"/>
+      <c r="H3" s="72"/>
+      <c r="I3" s="72"/>
+      <c r="J3" s="72"/>
+      <c r="K3" s="72"/>
+      <c r="L3" s="72"/>
+      <c r="M3" s="73"/>
       <c r="N3" s="15"/>
       <c r="O3" s="10"/>
       <c r="P3" s="10"/>
       <c r="Q3" s="10"/>
       <c r="R3" s="10"/>
     </row>
-    <row r="4" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="76" t="s">
+    <row r="4" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="81" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="72" t="s">
+      <c r="B4" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="73"/>
-      <c r="D4" s="72" t="s">
+      <c r="C4" s="78"/>
+      <c r="D4" s="77" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="73"/>
+      <c r="E4" s="78"/>
       <c r="F4" s="63" t="s">
         <v>6</v>
       </c>
       <c r="G4" s="64"/>
       <c r="H4" s="64"/>
       <c r="I4" s="65"/>
-      <c r="J4" s="69" t="s">
+      <c r="J4" s="74" t="s">
         <v>18</v>
       </c>
-      <c r="K4" s="70"/>
-      <c r="L4" s="71"/>
+      <c r="K4" s="75"/>
+      <c r="L4" s="76"/>
       <c r="M4" s="60" t="s">
         <v>15</v>
       </c>
       <c r="N4" s="16"/>
     </row>
-    <row r="5" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="76"/>
+    <row r="5" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="81"/>
       <c r="B5" s="58" t="s">
         <v>1</v>
       </c>
@@ -2299,20 +2348,20 @@
       <c r="I5" s="58" t="s">
         <v>10</v>
       </c>
-      <c r="J5" s="74" t="s">
+      <c r="J5" s="79" t="s">
         <v>1</v>
       </c>
-      <c r="K5" s="74" t="s">
+      <c r="K5" s="79" t="s">
         <v>16</v>
       </c>
-      <c r="L5" s="74" t="s">
+      <c r="L5" s="79" t="s">
         <v>17</v>
       </c>
       <c r="M5" s="61"/>
       <c r="N5" s="15"/>
     </row>
-    <row r="6" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="77"/>
+    <row r="6" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="82"/>
       <c r="B6" s="59"/>
       <c r="C6" s="59"/>
       <c r="D6" s="59"/>
@@ -2327,9 +2376,9 @@
         <v>13</v>
       </c>
       <c r="I6" s="59"/>
-      <c r="J6" s="75"/>
-      <c r="K6" s="75"/>
-      <c r="L6" s="75"/>
+      <c r="J6" s="80"/>
+      <c r="K6" s="80"/>
+      <c r="L6" s="80"/>
       <c r="M6" s="62"/>
       <c r="N6" s="15"/>
     </row>
@@ -2356,21 +2405,21 @@
       <c r="R7" s="30"/>
     </row>
     <row r="8" spans="1:19" s="14" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="95" t="s">
+      <c r="A8" s="89" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="96"/>
-      <c r="C8" s="96"/>
-      <c r="D8" s="96"/>
-      <c r="E8" s="96"/>
-      <c r="F8" s="96"/>
-      <c r="G8" s="96"/>
-      <c r="H8" s="96"/>
-      <c r="I8" s="96"/>
-      <c r="J8" s="96"/>
-      <c r="K8" s="96"/>
-      <c r="L8" s="96"/>
-      <c r="M8" s="97"/>
+      <c r="B8" s="90"/>
+      <c r="C8" s="90"/>
+      <c r="D8" s="90"/>
+      <c r="E8" s="90"/>
+      <c r="F8" s="90"/>
+      <c r="G8" s="90"/>
+      <c r="H8" s="90"/>
+      <c r="I8" s="90"/>
+      <c r="J8" s="90"/>
+      <c r="K8" s="90"/>
+      <c r="L8" s="90"/>
+      <c r="M8" s="91"/>
       <c r="N8" s="12"/>
       <c r="O8" s="12"/>
       <c r="P8" s="12"/>
@@ -2379,21 +2428,21 @@
       <c r="S8" s="13"/>
     </row>
     <row r="9" spans="1:19" s="14" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="86" t="s">
+      <c r="A9" s="66" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="87"/>
-      <c r="C9" s="87"/>
-      <c r="D9" s="87"/>
-      <c r="E9" s="87"/>
-      <c r="F9" s="87"/>
-      <c r="G9" s="87"/>
-      <c r="H9" s="87"/>
-      <c r="I9" s="87"/>
-      <c r="J9" s="87"/>
-      <c r="K9" s="87"/>
-      <c r="L9" s="87"/>
-      <c r="M9" s="88"/>
+      <c r="B9" s="67"/>
+      <c r="C9" s="67"/>
+      <c r="D9" s="67"/>
+      <c r="E9" s="67"/>
+      <c r="F9" s="67"/>
+      <c r="G9" s="67"/>
+      <c r="H9" s="67"/>
+      <c r="I9" s="67"/>
+      <c r="J9" s="67"/>
+      <c r="K9" s="67"/>
+      <c r="L9" s="67"/>
+      <c r="M9" s="68"/>
       <c r="N9" s="12"/>
       <c r="O9" s="12"/>
       <c r="P9" s="12"/>
@@ -2402,21 +2451,21 @@
       <c r="S9" s="13"/>
     </row>
     <row r="10" spans="1:19" s="14" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="86" t="s">
+      <c r="A10" s="66" t="s">
         <v>22</v>
       </c>
-      <c r="B10" s="87"/>
-      <c r="C10" s="87"/>
-      <c r="D10" s="87"/>
-      <c r="E10" s="87"/>
-      <c r="F10" s="87"/>
-      <c r="G10" s="87"/>
-      <c r="H10" s="87"/>
-      <c r="I10" s="87"/>
-      <c r="J10" s="87"/>
-      <c r="K10" s="87"/>
-      <c r="L10" s="87"/>
-      <c r="M10" s="88"/>
+      <c r="B10" s="67"/>
+      <c r="C10" s="67"/>
+      <c r="D10" s="67"/>
+      <c r="E10" s="67"/>
+      <c r="F10" s="67"/>
+      <c r="G10" s="67"/>
+      <c r="H10" s="67"/>
+      <c r="I10" s="67"/>
+      <c r="J10" s="67"/>
+      <c r="K10" s="67"/>
+      <c r="L10" s="67"/>
+      <c r="M10" s="68"/>
       <c r="N10" s="12"/>
       <c r="O10" s="12"/>
       <c r="P10" s="12"/>
@@ -2425,21 +2474,21 @@
       <c r="S10" s="13"/>
     </row>
     <row r="11" spans="1:19" s="14" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="86" t="s">
-        <v>29</v>
-      </c>
-      <c r="B11" s="87"/>
-      <c r="C11" s="87"/>
-      <c r="D11" s="87"/>
-      <c r="E11" s="87"/>
-      <c r="F11" s="87"/>
-      <c r="G11" s="87"/>
-      <c r="H11" s="87"/>
-      <c r="I11" s="87"/>
-      <c r="J11" s="87"/>
-      <c r="K11" s="87"/>
-      <c r="L11" s="87"/>
-      <c r="M11" s="88"/>
+      <c r="A11" s="66" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="67"/>
+      <c r="C11" s="67"/>
+      <c r="D11" s="67"/>
+      <c r="E11" s="67"/>
+      <c r="F11" s="67"/>
+      <c r="G11" s="67"/>
+      <c r="H11" s="67"/>
+      <c r="I11" s="67"/>
+      <c r="J11" s="67"/>
+      <c r="K11" s="67"/>
+      <c r="L11" s="67"/>
+      <c r="M11" s="68"/>
       <c r="N11" s="12"/>
       <c r="O11" s="12"/>
       <c r="P11" s="12"/>
@@ -2447,22 +2496,22 @@
       <c r="R11" s="12"/>
       <c r="S11" s="13"/>
     </row>
-    <row r="12" spans="1:19" s="14" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="86" t="s">
+    <row r="12" spans="1:19" s="14" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="66" t="s">
         <v>23</v>
       </c>
-      <c r="B12" s="87"/>
-      <c r="C12" s="87"/>
-      <c r="D12" s="87"/>
-      <c r="E12" s="87"/>
-      <c r="F12" s="87"/>
-      <c r="G12" s="87"/>
-      <c r="H12" s="87"/>
-      <c r="I12" s="87"/>
-      <c r="J12" s="87"/>
-      <c r="K12" s="87"/>
-      <c r="L12" s="87"/>
-      <c r="M12" s="88"/>
+      <c r="B12" s="67"/>
+      <c r="C12" s="67"/>
+      <c r="D12" s="67"/>
+      <c r="E12" s="67"/>
+      <c r="F12" s="67"/>
+      <c r="G12" s="67"/>
+      <c r="H12" s="67"/>
+      <c r="I12" s="67"/>
+      <c r="J12" s="67"/>
+      <c r="K12" s="67"/>
+      <c r="L12" s="67"/>
+      <c r="M12" s="68"/>
       <c r="N12" s="12"/>
       <c r="O12" s="12"/>
       <c r="P12" s="12"/>
@@ -2470,9 +2519,9 @@
       <c r="R12" s="12"/>
       <c r="S12" s="13"/>
     </row>
-    <row r="13" spans="1:19" s="54" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:19" s="54" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="55" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B13" s="56"/>
       <c r="C13" s="56"/>
@@ -2493,9 +2542,9 @@
       <c r="R13" s="52"/>
       <c r="S13" s="53"/>
     </row>
-    <row r="14" spans="1:19" s="54" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:19" s="54" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="55" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B14" s="56"/>
       <c r="C14" s="56"/>
@@ -2516,47 +2565,47 @@
       <c r="R14" s="52"/>
       <c r="S14" s="53"/>
     </row>
-    <row r="15" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="89" t="s">
+    <row r="15" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="83" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="90"/>
-      <c r="C15" s="90"/>
-      <c r="D15" s="90"/>
-      <c r="E15" s="90"/>
-      <c r="F15" s="90"/>
-      <c r="G15" s="90"/>
-      <c r="H15" s="90"/>
-      <c r="I15" s="90"/>
-      <c r="J15" s="90"/>
-      <c r="K15" s="90"/>
-      <c r="L15" s="90"/>
-      <c r="M15" s="91"/>
+      <c r="B15" s="84"/>
+      <c r="C15" s="84"/>
+      <c r="D15" s="84"/>
+      <c r="E15" s="84"/>
+      <c r="F15" s="84"/>
+      <c r="G15" s="84"/>
+      <c r="H15" s="84"/>
+      <c r="I15" s="84"/>
+      <c r="J15" s="84"/>
+      <c r="K15" s="84"/>
+      <c r="L15" s="84"/>
+      <c r="M15" s="85"/>
       <c r="N15" s="15"/>
     </row>
-    <row r="16" spans="1:19" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A16" s="76" t="s">
+    <row r="16" spans="1:19" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="81" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="84" t="s">
+      <c r="B16" s="69" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="85"/>
-      <c r="D16" s="84" t="s">
+      <c r="C16" s="70"/>
+      <c r="D16" s="69" t="s">
         <v>5</v>
       </c>
-      <c r="E16" s="85"/>
-      <c r="F16" s="80" t="s">
+      <c r="E16" s="70"/>
+      <c r="F16" s="97" t="s">
         <v>6</v>
       </c>
-      <c r="G16" s="81"/>
-      <c r="H16" s="81"/>
-      <c r="I16" s="82"/>
-      <c r="J16" s="92" t="s">
+      <c r="G16" s="98"/>
+      <c r="H16" s="98"/>
+      <c r="I16" s="99"/>
+      <c r="J16" s="86" t="s">
         <v>14</v>
       </c>
-      <c r="K16" s="93"/>
-      <c r="L16" s="94"/>
+      <c r="K16" s="87"/>
+      <c r="L16" s="88"/>
       <c r="M16" s="60" t="s">
         <v>15</v>
       </c>
@@ -2566,35 +2615,35 @@
       <c r="Q16" s="11"/>
       <c r="R16" s="11"/>
     </row>
-    <row r="17" spans="1:18" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="76"/>
-      <c r="B17" s="78" t="s">
+    <row r="17" spans="1:18" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="81"/>
+      <c r="B17" s="95" t="s">
         <v>1</v>
       </c>
-      <c r="C17" s="78" t="s">
+      <c r="C17" s="95" t="s">
         <v>0</v>
       </c>
-      <c r="D17" s="78" t="s">
+      <c r="D17" s="95" t="s">
         <v>7</v>
       </c>
-      <c r="E17" s="78" t="s">
+      <c r="E17" s="95" t="s">
         <v>8</v>
       </c>
-      <c r="F17" s="80" t="s">
+      <c r="F17" s="97" t="s">
         <v>9</v>
       </c>
-      <c r="G17" s="81"/>
-      <c r="H17" s="82"/>
-      <c r="I17" s="78" t="s">
+      <c r="G17" s="98"/>
+      <c r="H17" s="99"/>
+      <c r="I17" s="95" t="s">
         <v>10</v>
       </c>
-      <c r="J17" s="99" t="s">
+      <c r="J17" s="93" t="s">
         <v>1</v>
       </c>
-      <c r="K17" s="99" t="s">
+      <c r="K17" s="93" t="s">
         <v>16</v>
       </c>
-      <c r="L17" s="99" t="s">
+      <c r="L17" s="93" t="s">
         <v>17</v>
       </c>
       <c r="M17" s="61"/>
@@ -2604,12 +2653,12 @@
       <c r="Q17" s="11"/>
       <c r="R17" s="11"/>
     </row>
-    <row r="18" spans="1:18" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="83"/>
-      <c r="B18" s="79"/>
-      <c r="C18" s="79"/>
-      <c r="D18" s="79"/>
-      <c r="E18" s="79"/>
+    <row r="18" spans="1:18" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="100"/>
+      <c r="B18" s="96"/>
+      <c r="C18" s="96"/>
+      <c r="D18" s="96"/>
+      <c r="E18" s="96"/>
       <c r="F18" s="19" t="s">
         <v>11</v>
       </c>
@@ -2619,14 +2668,14 @@
       <c r="H18" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="I18" s="79"/>
-      <c r="J18" s="100"/>
-      <c r="K18" s="100"/>
-      <c r="L18" s="100"/>
-      <c r="M18" s="98"/>
+      <c r="I18" s="96"/>
+      <c r="J18" s="94"/>
+      <c r="K18" s="94"/>
+      <c r="L18" s="94"/>
+      <c r="M18" s="92"/>
       <c r="N18" s="15"/>
     </row>
-    <row r="19" spans="1:18" s="38" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:18" s="38" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A19" s="32"/>
       <c r="B19" s="33"/>
       <c r="C19" s="18"/>
@@ -2646,7 +2695,7 @@
       <c r="Q19" s="30"/>
       <c r="R19" s="30"/>
     </row>
-    <row r="20" spans="1:18" s="38" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:18" s="38" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A20" s="39"/>
       <c r="B20" s="46"/>
       <c r="C20" s="47"/>
@@ -2666,7 +2715,7 @@
       <c r="Q20" s="30"/>
       <c r="R20" s="30"/>
     </row>
-    <row r="21" spans="1:18" s="38" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:18" s="38" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A21" s="39"/>
       <c r="B21" s="46"/>
       <c r="C21" s="47"/>
@@ -2686,7 +2735,7 @@
       <c r="Q21" s="30"/>
       <c r="R21" s="30"/>
     </row>
-    <row r="22" spans="1:18" s="38" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:18" s="38" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A22" s="39"/>
       <c r="B22" s="46"/>
       <c r="C22" s="47"/>
@@ -2706,7 +2755,7 @@
       <c r="Q22" s="30"/>
       <c r="R22" s="30"/>
     </row>
-    <row r="23" spans="1:18" s="38" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:18" s="38" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A23" s="39"/>
       <c r="B23" s="46"/>
       <c r="C23" s="47"/>
@@ -2726,7 +2775,7 @@
       <c r="Q23" s="30"/>
       <c r="R23" s="30"/>
     </row>
-    <row r="24" spans="1:18" s="38" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:18" s="38" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A24" s="39"/>
       <c r="B24" s="46"/>
       <c r="C24" s="47"/>
@@ -2746,7 +2795,7 @@
       <c r="Q24" s="30"/>
       <c r="R24" s="30"/>
     </row>
-    <row r="25" spans="1:18" s="38" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:18" s="38" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A25" s="39"/>
       <c r="B25" s="46"/>
       <c r="C25" s="46"/>
@@ -2766,7 +2815,7 @@
       <c r="Q25" s="30"/>
       <c r="R25" s="30"/>
     </row>
-    <row r="26" spans="1:18" s="38" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:18" s="38" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A26" s="39"/>
       <c r="B26" s="46"/>
       <c r="C26" s="46"/>
@@ -2786,7 +2835,7 @@
       <c r="Q26" s="30"/>
       <c r="R26" s="30"/>
     </row>
-    <row r="27" spans="1:18" s="38" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:18" s="38" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A27" s="39"/>
       <c r="B27" s="46"/>
       <c r="C27" s="46"/>
@@ -2806,7 +2855,7 @@
       <c r="Q27" s="30"/>
       <c r="R27" s="30"/>
     </row>
-    <row r="28" spans="1:18" s="38" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:18" s="38" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A28" s="39"/>
       <c r="B28" s="46"/>
       <c r="C28" s="46"/>
@@ -2826,7 +2875,7 @@
       <c r="Q28" s="30"/>
       <c r="R28" s="30"/>
     </row>
-    <row r="29" spans="1:18" s="38" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:18" s="38" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A29" s="39"/>
       <c r="B29" s="46"/>
       <c r="C29" s="46"/>
@@ -2846,7 +2895,7 @@
       <c r="Q29" s="30"/>
       <c r="R29" s="30"/>
     </row>
-    <row r="30" spans="1:18" s="38" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:18" s="38" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A30" s="39"/>
       <c r="B30" s="46"/>
       <c r="C30" s="46"/>
@@ -2866,7 +2915,7 @@
       <c r="Q30" s="30"/>
       <c r="R30" s="30"/>
     </row>
-    <row r="31" spans="1:18" s="38" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:18" s="38" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A31" s="39"/>
       <c r="B31" s="46"/>
       <c r="C31" s="46"/>
@@ -2886,7 +2935,7 @@
       <c r="Q31" s="30"/>
       <c r="R31" s="30"/>
     </row>
-    <row r="32" spans="1:18" s="38" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:18" s="38" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A32" s="39"/>
       <c r="B32" s="46"/>
       <c r="C32" s="46"/>
@@ -2906,7 +2955,7 @@
       <c r="Q32" s="30"/>
       <c r="R32" s="30"/>
     </row>
-    <row r="33" spans="1:18" s="38" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:18" s="38" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A33" s="39"/>
       <c r="B33" s="46"/>
       <c r="C33" s="46"/>
@@ -2926,7 +2975,7 @@
       <c r="Q33" s="30"/>
       <c r="R33" s="30"/>
     </row>
-    <row r="34" spans="1:18" s="38" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:18" s="38" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A34" s="39"/>
       <c r="B34" s="46"/>
       <c r="C34" s="46"/>
@@ -2946,7 +2995,7 @@
       <c r="Q34" s="30"/>
       <c r="R34" s="30"/>
     </row>
-    <row r="35" spans="1:18" s="38" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:18" s="38" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A35" s="39"/>
       <c r="B35" s="46"/>
       <c r="C35" s="46"/>
@@ -2966,7 +3015,7 @@
       <c r="Q35" s="30"/>
       <c r="R35" s="30"/>
     </row>
-    <row r="36" spans="1:18" s="38" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:18" s="38" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A36" s="39"/>
       <c r="B36" s="46"/>
       <c r="C36" s="46"/>
@@ -2986,7 +3035,7 @@
       <c r="Q36" s="30"/>
       <c r="R36" s="30"/>
     </row>
-    <row r="37" spans="1:18" s="38" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:18" s="38" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A37" s="39"/>
       <c r="B37" s="46"/>
       <c r="C37" s="46"/>
@@ -3006,7 +3055,7 @@
       <c r="Q37" s="30"/>
       <c r="R37" s="30"/>
     </row>
-    <row r="38" spans="1:18" s="38" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:18" s="38" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A38" s="39"/>
       <c r="B38" s="46"/>
       <c r="C38" s="46"/>
@@ -3026,7 +3075,7 @@
       <c r="Q38" s="30"/>
       <c r="R38" s="30"/>
     </row>
-    <row r="39" spans="1:18" s="38" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:18" s="38" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A39" s="39"/>
       <c r="B39" s="46"/>
       <c r="C39" s="46"/>
@@ -3046,7 +3095,7 @@
       <c r="Q39" s="30"/>
       <c r="R39" s="30"/>
     </row>
-    <row r="40" spans="1:18" s="38" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:18" s="38" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A40" s="39"/>
       <c r="B40" s="46"/>
       <c r="C40" s="46"/>
@@ -3066,7 +3115,7 @@
       <c r="Q40" s="30"/>
       <c r="R40" s="30"/>
     </row>
-    <row r="41" spans="1:18" s="38" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:18" s="38" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A41" s="39"/>
       <c r="B41" s="46"/>
       <c r="C41" s="46"/>
@@ -3086,7 +3135,7 @@
       <c r="Q41" s="30"/>
       <c r="R41" s="30"/>
     </row>
-    <row r="42" spans="1:18" s="38" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:18" s="38" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A42" s="39"/>
       <c r="B42" s="46"/>
       <c r="C42" s="46"/>
@@ -3106,7 +3155,7 @@
       <c r="Q42" s="30"/>
       <c r="R42" s="30"/>
     </row>
-    <row r="43" spans="1:18" s="38" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:18" s="38" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A43" s="39"/>
       <c r="B43" s="46"/>
       <c r="C43" s="46"/>
@@ -3126,7 +3175,7 @@
       <c r="Q43" s="30"/>
       <c r="R43" s="30"/>
     </row>
-    <row r="44" spans="1:18" s="38" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:18" s="38" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A44" s="39"/>
       <c r="B44" s="46"/>
       <c r="C44" s="46"/>
@@ -3146,7 +3195,7 @@
       <c r="Q44" s="30"/>
       <c r="R44" s="30"/>
     </row>
-    <row r="45" spans="1:18" s="38" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:18" s="38" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A45" s="39"/>
       <c r="B45" s="46"/>
       <c r="C45" s="46"/>
@@ -3166,7 +3215,7 @@
       <c r="Q45" s="30"/>
       <c r="R45" s="30"/>
     </row>
-    <row r="46" spans="1:18" s="38" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:18" s="38" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A46" s="39"/>
       <c r="B46" s="46"/>
       <c r="C46" s="46"/>
@@ -3186,7 +3235,7 @@
       <c r="Q46" s="30"/>
       <c r="R46" s="30"/>
     </row>
-    <row r="47" spans="1:18" s="38" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:18" s="38" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A47" s="39"/>
       <c r="B47" s="46"/>
       <c r="C47" s="46"/>
@@ -3206,7 +3255,7 @@
       <c r="Q47" s="30"/>
       <c r="R47" s="30"/>
     </row>
-    <row r="48" spans="1:18" s="38" customFormat="1" ht="13.15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:18" s="38" customFormat="1" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A48" s="42"/>
       <c r="B48" s="43"/>
       <c r="C48" s="43"/>
@@ -3226,7 +3275,7 @@
       <c r="Q48" s="30"/>
       <c r="R48" s="30"/>
     </row>
-    <row r="49" spans="11:12" x14ac:dyDescent="0.35">
+    <row r="49" spans="11:12" x14ac:dyDescent="0.2">
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
     </row>
@@ -3278,15 +3327,15 @@
     <mergeCell ref="A12:M12"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F15 F7 F19:F1048576 F3">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F15 F7 F19:F1048576 F3" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>1</formula1>
       <formula2>31</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G15 G7 G19:G1048576 G3">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G15 G7 G19:G1048576 G3" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>1</formula1>
       <formula2>12</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H19:H1048576 H7 H15 H3">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H19:H1048576 H7 H15 H3" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>1900</formula1>
       <formula2>2100</formula2>
     </dataValidation>
